--- a/output/Laporan_Arah_Validasi_2025.xlsx
+++ b/output/Laporan_Arah_Validasi_2025.xlsx
@@ -474,16 +474,16 @@
         <v>45985.15302083334</v>
       </c>
       <c r="B2" t="n">
-        <v>-7.986112910910143</v>
+        <v>-7.977602926040744</v>
       </c>
       <c r="C2" t="n">
-        <v>113.4167560065577</v>
+        <v>113.4222419331524</v>
       </c>
       <c r="D2" t="n">
-        <v>246.8463597035008</v>
+        <v>246.5272061661201</v>
       </c>
       <c r="E2" t="n">
-        <v>203.1211566925049</v>
+        <v>191.9799470901489</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -499,16 +499,16 @@
         <v>46049.34773148148</v>
       </c>
       <c r="B3" t="n">
-        <v>-7.986112910910143</v>
+        <v>-7.977602926040744</v>
       </c>
       <c r="C3" t="n">
-        <v>113.4167560065577</v>
+        <v>113.4222419331524</v>
       </c>
       <c r="D3" t="n">
-        <v>246.8463597035008</v>
+        <v>246.5272061661201</v>
       </c>
       <c r="E3" t="n">
-        <v>188.0237746238708</v>
+        <v>183.9334917068481</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>

--- a/output/Laporan_Arah_Validasi_2025.xlsx
+++ b/output/Laporan_Arah_Validasi_2025.xlsx
@@ -474,16 +474,16 @@
         <v>45985.15302083334</v>
       </c>
       <c r="B2" t="n">
-        <v>-7.977602926040744</v>
+        <v>-7.986112910910143</v>
       </c>
       <c r="C2" t="n">
-        <v>113.4222419331524</v>
+        <v>113.4167560065577</v>
       </c>
       <c r="D2" t="n">
-        <v>246.5272061661201</v>
+        <v>246.8463597035008</v>
       </c>
       <c r="E2" t="n">
-        <v>191.9799470901489</v>
+        <v>194.298791885376</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -499,16 +499,16 @@
         <v>46049.34773148148</v>
       </c>
       <c r="B3" t="n">
-        <v>-7.977602926040744</v>
+        <v>-7.986112910910143</v>
       </c>
       <c r="C3" t="n">
-        <v>113.4222419331524</v>
+        <v>113.4167560065577</v>
       </c>
       <c r="D3" t="n">
-        <v>246.5272061661201</v>
+        <v>246.8463597035008</v>
       </c>
       <c r="E3" t="n">
-        <v>183.9334917068481</v>
+        <v>175.9845077991486</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>

--- a/output/Laporan_Arah_Validasi_2025.xlsx
+++ b/output/Laporan_Arah_Validasi_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -474,20 +474,20 @@
         <v>45985.15302083334</v>
       </c>
       <c r="B2" t="n">
-        <v>-7.986112910910143</v>
+        <v>-7.989012876971192</v>
       </c>
       <c r="C2" t="n">
-        <v>113.4167560065577</v>
+        <v>113.4288015660753</v>
       </c>
       <c r="D2" t="n">
-        <v>246.8463597035008</v>
+        <v>247.9585070761894</v>
       </c>
       <c r="E2" t="n">
-        <v>194.298791885376</v>
+        <v>207.2229623794556</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Selatan</t>
+          <t>Barat Daya</t>
         </is>
       </c>
       <c r="G2" t="b">
@@ -496,26 +496,226 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46049.34773148148</v>
+        <v>45985.15302083334</v>
       </c>
       <c r="B3" t="n">
-        <v>-7.986112910910143</v>
+        <v>-7.989012876971192</v>
       </c>
       <c r="C3" t="n">
-        <v>113.4167560065577</v>
+        <v>113.4288015660753</v>
       </c>
       <c r="D3" t="n">
-        <v>246.8463597035008</v>
+        <v>247.9585070761894</v>
       </c>
       <c r="E3" t="n">
-        <v>175.9845077991486</v>
+        <v>207.2229623794556</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Selatan</t>
+          <t>Barat Daya</t>
         </is>
       </c>
       <c r="G3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>45985.15302083334</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-7.989012876971192</v>
+      </c>
+      <c r="C4" t="n">
+        <v>113.4288015660753</v>
+      </c>
+      <c r="D4" t="n">
+        <v>247.9585070761894</v>
+      </c>
+      <c r="E4" t="n">
+        <v>207.2229623794556</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Barat Daya</t>
+        </is>
+      </c>
+      <c r="G4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>45985.15302083334</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-7.989012876971192</v>
+      </c>
+      <c r="C5" t="n">
+        <v>113.4288015660753</v>
+      </c>
+      <c r="D5" t="n">
+        <v>247.9585070761894</v>
+      </c>
+      <c r="E5" t="n">
+        <v>207.2229623794556</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Barat Daya</t>
+        </is>
+      </c>
+      <c r="G5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>45985.15302083334</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-7.989012876971192</v>
+      </c>
+      <c r="C6" t="n">
+        <v>113.4288015660753</v>
+      </c>
+      <c r="D6" t="n">
+        <v>247.9585070761894</v>
+      </c>
+      <c r="E6" t="n">
+        <v>207.2229623794556</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Barat Daya</t>
+        </is>
+      </c>
+      <c r="G6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>45985.15302083334</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-7.989012876971192</v>
+      </c>
+      <c r="C7" t="n">
+        <v>113.4288015660753</v>
+      </c>
+      <c r="D7" t="n">
+        <v>247.9585070761894</v>
+      </c>
+      <c r="E7" t="n">
+        <v>207.2229623794556</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Barat Daya</t>
+        </is>
+      </c>
+      <c r="G7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>45985.15302083334</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-7.989012876971192</v>
+      </c>
+      <c r="C8" t="n">
+        <v>113.4288015660753</v>
+      </c>
+      <c r="D8" t="n">
+        <v>247.9585070761894</v>
+      </c>
+      <c r="E8" t="n">
+        <v>207.2229623794556</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Barat Daya</t>
+        </is>
+      </c>
+      <c r="G8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>45985.15302083334</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-7.989012876971192</v>
+      </c>
+      <c r="C9" t="n">
+        <v>113.4288015660753</v>
+      </c>
+      <c r="D9" t="n">
+        <v>247.9585070761894</v>
+      </c>
+      <c r="E9" t="n">
+        <v>207.2229623794556</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Barat Daya</t>
+        </is>
+      </c>
+      <c r="G9" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>45985.15302083334</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-7.989012876971192</v>
+      </c>
+      <c r="C10" t="n">
+        <v>113.4288015660753</v>
+      </c>
+      <c r="D10" t="n">
+        <v>247.9585070761894</v>
+      </c>
+      <c r="E10" t="n">
+        <v>207.2229623794556</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Barat Daya</t>
+        </is>
+      </c>
+      <c r="G10" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>45985.15302083334</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-7.989012876971192</v>
+      </c>
+      <c r="C11" t="n">
+        <v>113.4288015660753</v>
+      </c>
+      <c r="D11" t="n">
+        <v>247.9585070761894</v>
+      </c>
+      <c r="E11" t="n">
+        <v>207.2229623794556</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Barat Daya</t>
+        </is>
+      </c>
+      <c r="G11" t="b">
         <v>0</v>
       </c>
     </row>

--- a/output/Laporan_Arah_Validasi_2025.xlsx
+++ b/output/Laporan_Arah_Validasi_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -474,248 +474,23 @@
         <v>45985.15302083334</v>
       </c>
       <c r="B2" t="n">
-        <v>-7.989012876971192</v>
+        <v>-7.980989204487446</v>
       </c>
       <c r="C2" t="n">
-        <v>113.4288015660753</v>
+        <v>113.4538423501609</v>
       </c>
       <c r="D2" t="n">
-        <v>247.9585070761894</v>
+        <v>249.1080365175825</v>
       </c>
       <c r="E2" t="n">
-        <v>207.2229623794556</v>
+        <v>191.9097375869751</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Barat Daya</t>
+          <t>Selatan</t>
         </is>
       </c>
       <c r="G2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="n">
-        <v>45985.15302083334</v>
-      </c>
-      <c r="B3" t="n">
-        <v>-7.989012876971192</v>
-      </c>
-      <c r="C3" t="n">
-        <v>113.4288015660753</v>
-      </c>
-      <c r="D3" t="n">
-        <v>247.9585070761894</v>
-      </c>
-      <c r="E3" t="n">
-        <v>207.2229623794556</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Barat Daya</t>
-        </is>
-      </c>
-      <c r="G3" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="n">
-        <v>45985.15302083334</v>
-      </c>
-      <c r="B4" t="n">
-        <v>-7.989012876971192</v>
-      </c>
-      <c r="C4" t="n">
-        <v>113.4288015660753</v>
-      </c>
-      <c r="D4" t="n">
-        <v>247.9585070761894</v>
-      </c>
-      <c r="E4" t="n">
-        <v>207.2229623794556</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Barat Daya</t>
-        </is>
-      </c>
-      <c r="G4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="n">
-        <v>45985.15302083334</v>
-      </c>
-      <c r="B5" t="n">
-        <v>-7.989012876971192</v>
-      </c>
-      <c r="C5" t="n">
-        <v>113.4288015660753</v>
-      </c>
-      <c r="D5" t="n">
-        <v>247.9585070761894</v>
-      </c>
-      <c r="E5" t="n">
-        <v>207.2229623794556</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Barat Daya</t>
-        </is>
-      </c>
-      <c r="G5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="n">
-        <v>45985.15302083334</v>
-      </c>
-      <c r="B6" t="n">
-        <v>-7.989012876971192</v>
-      </c>
-      <c r="C6" t="n">
-        <v>113.4288015660753</v>
-      </c>
-      <c r="D6" t="n">
-        <v>247.9585070761894</v>
-      </c>
-      <c r="E6" t="n">
-        <v>207.2229623794556</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Barat Daya</t>
-        </is>
-      </c>
-      <c r="G6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="n">
-        <v>45985.15302083334</v>
-      </c>
-      <c r="B7" t="n">
-        <v>-7.989012876971192</v>
-      </c>
-      <c r="C7" t="n">
-        <v>113.4288015660753</v>
-      </c>
-      <c r="D7" t="n">
-        <v>247.9585070761894</v>
-      </c>
-      <c r="E7" t="n">
-        <v>207.2229623794556</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Barat Daya</t>
-        </is>
-      </c>
-      <c r="G7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="n">
-        <v>45985.15302083334</v>
-      </c>
-      <c r="B8" t="n">
-        <v>-7.989012876971192</v>
-      </c>
-      <c r="C8" t="n">
-        <v>113.4288015660753</v>
-      </c>
-      <c r="D8" t="n">
-        <v>247.9585070761894</v>
-      </c>
-      <c r="E8" t="n">
-        <v>207.2229623794556</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Barat Daya</t>
-        </is>
-      </c>
-      <c r="G8" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="n">
-        <v>45985.15302083334</v>
-      </c>
-      <c r="B9" t="n">
-        <v>-7.989012876971192</v>
-      </c>
-      <c r="C9" t="n">
-        <v>113.4288015660753</v>
-      </c>
-      <c r="D9" t="n">
-        <v>247.9585070761894</v>
-      </c>
-      <c r="E9" t="n">
-        <v>207.2229623794556</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Barat Daya</t>
-        </is>
-      </c>
-      <c r="G9" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="n">
-        <v>45985.15302083334</v>
-      </c>
-      <c r="B10" t="n">
-        <v>-7.989012876971192</v>
-      </c>
-      <c r="C10" t="n">
-        <v>113.4288015660753</v>
-      </c>
-      <c r="D10" t="n">
-        <v>247.9585070761894</v>
-      </c>
-      <c r="E10" t="n">
-        <v>207.2229623794556</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Barat Daya</t>
-        </is>
-      </c>
-      <c r="G10" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="n">
-        <v>45985.15302083334</v>
-      </c>
-      <c r="B11" t="n">
-        <v>-7.989012876971192</v>
-      </c>
-      <c r="C11" t="n">
-        <v>113.4288015660753</v>
-      </c>
-      <c r="D11" t="n">
-        <v>247.9585070761894</v>
-      </c>
-      <c r="E11" t="n">
-        <v>207.2229623794556</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Barat Daya</t>
-        </is>
-      </c>
-      <c r="G11" t="b">
         <v>0</v>
       </c>
     </row>

--- a/output/Laporan_Arah_Validasi_2025.xlsx
+++ b/output/Laporan_Arah_Validasi_2025.xlsx
@@ -474,16 +474,16 @@
         <v>45985.15302083334</v>
       </c>
       <c r="B2" t="n">
-        <v>-7.980989204487446</v>
+        <v>-7.983215942445002</v>
       </c>
       <c r="C2" t="n">
-        <v>113.4538423501609</v>
+        <v>113.4180948185366</v>
       </c>
       <c r="D2" t="n">
-        <v>249.1080365175825</v>
+        <v>270.3989997287751</v>
       </c>
       <c r="E2" t="n">
-        <v>191.9097375869751</v>
+        <v>197.4300670623779</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>

--- a/output/Laporan_Arah_Validasi_2025.xlsx
+++ b/output/Laporan_Arah_Validasi_2025.xlsx
@@ -474,16 +474,16 @@
         <v>45985.15302083334</v>
       </c>
       <c r="B2" t="n">
-        <v>-7.983215942445002</v>
+        <v>-7.988805762624001</v>
       </c>
       <c r="C2" t="n">
-        <v>113.4180948185366</v>
+        <v>113.4566358314802</v>
       </c>
       <c r="D2" t="n">
-        <v>270.3989997287751</v>
+        <v>274.0080979183625</v>
       </c>
       <c r="E2" t="n">
-        <v>197.4300670623779</v>
+        <v>193.0121898651123</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>

--- a/output/Laporan_Arah_Validasi_2025.xlsx
+++ b/output/Laporan_Arah_Validasi_2025.xlsx
@@ -474,16 +474,16 @@
         <v>45985.15302083334</v>
       </c>
       <c r="B2" t="n">
-        <v>-7.988805762624001</v>
+        <v>-7.967502200723235</v>
       </c>
       <c r="C2" t="n">
-        <v>113.4566358314802</v>
+        <v>113.413704571108</v>
       </c>
       <c r="D2" t="n">
-        <v>274.0080979183625</v>
+        <v>270.6932928215665</v>
       </c>
       <c r="E2" t="n">
-        <v>193.0121898651123</v>
+        <v>189.7744417190552</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>

--- a/output/Laporan_Arah_Validasi_2025.xlsx
+++ b/output/Laporan_Arah_Validasi_2025.xlsx
@@ -474,16 +474,16 @@
         <v>45985.15302083334</v>
       </c>
       <c r="B2" t="n">
-        <v>-7.984918398815166</v>
+        <v>-7.960037874747122</v>
       </c>
       <c r="C2" t="n">
-        <v>113.4322254440981</v>
+        <v>113.4310427393131</v>
       </c>
       <c r="D2" t="n">
-        <v>271.7359380264079</v>
+        <v>272.7745055333937</v>
       </c>
       <c r="E2" t="n">
-        <v>202.3378872871399</v>
+        <v>186.2705326080322</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>

--- a/output/Laporan_Arah_Validasi_2025.xlsx
+++ b/output/Laporan_Arah_Validasi_2025.xlsx
@@ -474,16 +474,16 @@
         <v>45985.15302083334</v>
       </c>
       <c r="B2" t="n">
-        <v>-7.960037874747122</v>
+        <v>-7.983215942445002</v>
       </c>
       <c r="C2" t="n">
-        <v>113.4310427393131</v>
+        <v>113.4180948185366</v>
       </c>
       <c r="D2" t="n">
-        <v>272.7745055333937</v>
+        <v>270.3989997287751</v>
       </c>
       <c r="E2" t="n">
-        <v>186.2705326080322</v>
+        <v>194.3928623199463</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>

--- a/output/Laporan_Arah_Validasi_2025.xlsx
+++ b/output/Laporan_Arah_Validasi_2025.xlsx
@@ -474,16 +474,16 @@
         <v>45985.15302083334</v>
       </c>
       <c r="B2" t="n">
-        <v>-7.983215942445002</v>
+        <v>-7.986886135326065</v>
       </c>
       <c r="C2" t="n">
-        <v>113.4180948185366</v>
+        <v>113.4494951823272</v>
       </c>
       <c r="D2" t="n">
-        <v>270.3989997287751</v>
+        <v>273.3783106951117</v>
       </c>
       <c r="E2" t="n">
-        <v>194.3928623199463</v>
+        <v>202.3353338241577</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>

--- a/output/Laporan_Arah_Validasi_2025.xlsx
+++ b/output/Laporan_Arah_Validasi_2025.xlsx
@@ -474,16 +474,16 @@
         <v>45985.15302083334</v>
       </c>
       <c r="B2" t="n">
-        <v>-7.986886135326065</v>
+        <v>-7.992086549042218</v>
       </c>
       <c r="C2" t="n">
-        <v>113.4494951823272</v>
+        <v>113.4480030055188</v>
       </c>
       <c r="D2" t="n">
-        <v>273.3783106951117</v>
+        <v>272.9914306782712</v>
       </c>
       <c r="E2" t="n">
-        <v>202.3353338241577</v>
+        <v>181.0696649551392</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>

--- a/output/Laporan_Arah_Validasi_2025.xlsx
+++ b/output/Laporan_Arah_Validasi_2025.xlsx
@@ -474,16 +474,16 @@
         <v>45985.15302083334</v>
       </c>
       <c r="B2" t="n">
-        <v>-7.992086549042218</v>
+        <v>-8.028145758377896</v>
       </c>
       <c r="C2" t="n">
-        <v>113.4480030055188</v>
+        <v>113.5142652852997</v>
       </c>
       <c r="D2" t="n">
-        <v>272.9914306782712</v>
+        <v>278.0876561807677</v>
       </c>
       <c r="E2" t="n">
-        <v>181.0696649551392</v>
+        <v>193.3755970001221</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>

--- a/output/Laporan_Arah_Validasi_2025.xlsx
+++ b/output/Laporan_Arah_Validasi_2025.xlsx
@@ -474,16 +474,16 @@
         <v>45985.15302083334</v>
       </c>
       <c r="B2" t="n">
-        <v>-8.028145758377896</v>
+        <v>-7.98153482150245</v>
       </c>
       <c r="C2" t="n">
-        <v>113.5142652852997</v>
+        <v>113.4921796521939</v>
       </c>
       <c r="D2" t="n">
-        <v>278.0876561807677</v>
+        <v>278.615560389477</v>
       </c>
       <c r="E2" t="n">
-        <v>193.3755970001221</v>
+        <v>189.1371917724609</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
